--- a/artfynd/A 44496-2020 artfynd.xlsx
+++ b/artfynd/A 44496-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44496-2020 artfynd.xlsx
+++ b/artfynd/A 44496-2020 artfynd.xlsx
@@ -1592,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119539828</v>
+        <v>119539824</v>
       </c>
       <c r="B10" t="n">
-        <v>90846</v>
+        <v>91005</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,30 +1604,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578279</v>
+        <v>578362</v>
       </c>
       <c r="R10" t="n">
-        <v>6959126</v>
+        <v>6959147</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>olikåldrig, relativt gammal grannaturskog på småfuktig mark</t>
+          <t>olikåldrig, relativt gammal grannaturskog på sandig mark</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>förrötade granlågor</t>
+          <t>grov granlåga av vindfällt gammalt träd</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119539827</v>
+        <v>119539828</v>
       </c>
       <c r="B11" t="n">
         <v>90846</v>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578342</v>
+        <v>578279</v>
       </c>
       <c r="R11" t="n">
-        <v>6959176</v>
+        <v>6959126</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>förrötad grov granlåga</t>
+          <t>förrötade granlågor</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119539824</v>
+        <v>119539832</v>
       </c>
       <c r="B12" t="n">
-        <v>91005</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,25 +1844,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578362</v>
+        <v>578062</v>
       </c>
       <c r="R12" t="n">
-        <v>6959147</v>
+        <v>6959266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>olikåldrig, relativt gammal grannaturskog på sandig mark</t>
+          <t>olikåldrig, relativt gammal grannaturskog på småfuktig mark</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>grov granlåga av vindfällt gammalt träd</t>
+          <t>levande halvgammal gran</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119539832</v>
+        <v>119539829</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>86878</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578062</v>
+        <v>578191</v>
       </c>
       <c r="R13" t="n">
-        <v>6959266</v>
+        <v>6959226</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>levande halvgammal gran</t>
+          <t>grov granlåga av minst 200-årigt träd</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119539829</v>
+        <v>119539831</v>
       </c>
       <c r="B14" t="n">
-        <v>86878</v>
+        <v>91005</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,25 +2084,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578191</v>
+        <v>578231</v>
       </c>
       <c r="R14" t="n">
-        <v>6959226</v>
+        <v>6959283</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119539831</v>
+        <v>119539825</v>
       </c>
       <c r="B15" t="n">
-        <v>91005</v>
+        <v>95455</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2204,25 +2204,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578231</v>
+        <v>578400</v>
       </c>
       <c r="R15" t="n">
-        <v>6959283</v>
+        <v>6959170</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,12 +2285,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>olikåldrig, relativt gammal grannaturskog på småfuktig mark</t>
+          <t>olikåldrig, relativt gammal grannaturskog på sandig mark</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>grov granlåga av minst 200-årigt träd</t>
+          <t>äldre granvindfälle</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119539825</v>
+        <v>119539827</v>
       </c>
       <c r="B16" t="n">
-        <v>95455</v>
+        <v>90846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578400</v>
+        <v>578342</v>
       </c>
       <c r="R16" t="n">
-        <v>6959170</v>
+        <v>6959176</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>olikåldrig, relativt gammal grannaturskog på sandig mark</t>
+          <t>olikåldrig, relativt gammal grannaturskog på småfuktig mark</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>äldre granvindfälle</t>
+          <t>förrötad grov granlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 44496-2020 artfynd.xlsx
+++ b/artfynd/A 44496-2020 artfynd.xlsx
@@ -1592,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119539824</v>
+        <v>119539825</v>
       </c>
       <c r="B10" t="n">
-        <v>91005</v>
+        <v>95455</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,25 +1604,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578362</v>
+        <v>578400</v>
       </c>
       <c r="R10" t="n">
-        <v>6959147</v>
+        <v>6959170</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>grov granlåga av vindfällt gammalt träd</t>
+          <t>äldre granvindfälle</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119539828</v>
+        <v>119539831</v>
       </c>
       <c r="B11" t="n">
-        <v>90846</v>
+        <v>91005</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,30 +1724,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578279</v>
+        <v>578231</v>
       </c>
       <c r="R11" t="n">
-        <v>6959126</v>
+        <v>6959283</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>förrötade granlågor</t>
+          <t>grov granlåga av minst 200-årigt träd</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119539832</v>
+        <v>119539828</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>90846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,26 +1848,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578062</v>
+        <v>578279</v>
       </c>
       <c r="R12" t="n">
-        <v>6959266</v>
+        <v>6959126</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>levande halvgammal gran</t>
+          <t>förrötade granlågor</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119539829</v>
+        <v>119539827</v>
       </c>
       <c r="B13" t="n">
-        <v>86878</v>
+        <v>90846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578191</v>
+        <v>578342</v>
       </c>
       <c r="R13" t="n">
-        <v>6959226</v>
+        <v>6959176</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>grov granlåga av minst 200-årigt träd</t>
+          <t>förrötad grov granlåga</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119539831</v>
+        <v>119539832</v>
       </c>
       <c r="B14" t="n">
-        <v>91005</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,25 +2084,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578231</v>
+        <v>578062</v>
       </c>
       <c r="R14" t="n">
-        <v>6959283</v>
+        <v>6959266</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>grov granlåga av minst 200-årigt träd</t>
+          <t>levande halvgammal gran</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119539825</v>
+        <v>119539829</v>
       </c>
       <c r="B15" t="n">
-        <v>95455</v>
+        <v>86878</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2208,21 +2208,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578400</v>
+        <v>578191</v>
       </c>
       <c r="R15" t="n">
-        <v>6959170</v>
+        <v>6959226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,12 +2285,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>olikåldrig, relativt gammal grannaturskog på sandig mark</t>
+          <t>olikåldrig, relativt gammal grannaturskog på småfuktig mark</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>äldre granvindfälle</t>
+          <t>grov granlåga av minst 200-årigt träd</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119539827</v>
+        <v>119539824</v>
       </c>
       <c r="B16" t="n">
-        <v>90846</v>
+        <v>91005</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578342</v>
+        <v>578362</v>
       </c>
       <c r="R16" t="n">
-        <v>6959176</v>
+        <v>6959147</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>olikåldrig, relativt gammal grannaturskog på småfuktig mark</t>
+          <t>olikåldrig, relativt gammal grannaturskog på sandig mark</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>förrötad grov granlåga</t>
+          <t>grov granlåga av vindfällt gammalt träd</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
